--- a/artfynd/A 28515-2022 artfynd.xlsx
+++ b/artfynd/A 28515-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121142643</v>
+        <v>121142644</v>
       </c>
       <c r="B2" t="n">
-        <v>91998</v>
+        <v>97998</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479340</v>
+        <v>479335</v>
       </c>
       <c r="R2" t="n">
-        <v>6540076</v>
+        <v>6540083</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121142644</v>
+        <v>121142839</v>
       </c>
       <c r="B3" t="n">
-        <v>97988</v>
+        <v>97999</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>223591</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479335</v>
+        <v>479191</v>
       </c>
       <c r="R3" t="n">
-        <v>6540083</v>
+        <v>6540041</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121142839</v>
+        <v>121142653</v>
       </c>
       <c r="B4" t="n">
-        <v>97989</v>
+        <v>97999</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479191</v>
+        <v>479193</v>
       </c>
       <c r="R4" t="n">
-        <v>6540041</v>
+        <v>6540040</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121142653</v>
+        <v>121142643</v>
       </c>
       <c r="B5" t="n">
-        <v>97989</v>
+        <v>92008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,35 +1017,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223591</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1053,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479193</v>
+        <v>479340</v>
       </c>
       <c r="R5" t="n">
-        <v>6540040</v>
+        <v>6540076</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,6 +1096,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28515-2022 artfynd.xlsx
+++ b/artfynd/A 28515-2022 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121142839</v>
+        <v>121142643</v>
       </c>
       <c r="B3" t="n">
-        <v>97999</v>
+        <v>92008</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,35 +797,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223591</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479191</v>
+        <v>479340</v>
       </c>
       <c r="R3" t="n">
-        <v>6540041</v>
+        <v>6540076</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,6 +876,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121142643</v>
+        <v>121142839</v>
       </c>
       <c r="B5" t="n">
-        <v>92008</v>
+        <v>97999</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,34 +1017,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>223591</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1052,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479340</v>
+        <v>479191</v>
       </c>
       <c r="R5" t="n">
-        <v>6540076</v>
+        <v>6540041</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1097,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28515-2022 artfynd.xlsx
+++ b/artfynd/A 28515-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121142644</v>
       </c>
       <c r="B2" t="n">
-        <v>97998</v>
+        <v>98011</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>121142643</v>
       </c>
       <c r="B3" t="n">
-        <v>92008</v>
+        <v>92020</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>121142653</v>
       </c>
       <c r="B4" t="n">
-        <v>97999</v>
+        <v>98012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>121142839</v>
       </c>
       <c r="B5" t="n">
-        <v>97999</v>
+        <v>98012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 28515-2022 artfynd.xlsx
+++ b/artfynd/A 28515-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121142644</v>
+        <v>121142839</v>
       </c>
       <c r="B2" t="n">
-        <v>98011</v>
+        <v>98013</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>223591</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479335</v>
+        <v>479191</v>
       </c>
       <c r="R2" t="n">
-        <v>6540083</v>
+        <v>6540041</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121142643</v>
+        <v>121142644</v>
       </c>
       <c r="B3" t="n">
-        <v>92020</v>
+        <v>98012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -832,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479340</v>
+        <v>479335</v>
       </c>
       <c r="R3" t="n">
-        <v>6540076</v>
+        <v>6540083</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +877,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121142653</v>
+        <v>121142643</v>
       </c>
       <c r="B4" t="n">
-        <v>98012</v>
+        <v>92021</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,35 +907,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223591</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479193</v>
+        <v>479340</v>
       </c>
       <c r="R4" t="n">
-        <v>6540040</v>
+        <v>6540076</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,6 +986,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121142839</v>
+        <v>121142653</v>
       </c>
       <c r="B5" t="n">
-        <v>98012</v>
+        <v>98013</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479191</v>
+        <v>479193</v>
       </c>
       <c r="R5" t="n">
-        <v>6540041</v>
+        <v>6540040</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 28515-2022 artfynd.xlsx
+++ b/artfynd/A 28515-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121142839</v>
+        <v>121142643</v>
       </c>
       <c r="B2" t="n">
-        <v>98013</v>
+        <v>92024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223591</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479191</v>
+        <v>479340</v>
       </c>
       <c r="R2" t="n">
-        <v>6540041</v>
+        <v>6540076</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,6 +766,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121142644</v>
+        <v>121142653</v>
       </c>
       <c r="B3" t="n">
-        <v>98012</v>
+        <v>98016</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>223591</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479335</v>
+        <v>479193</v>
       </c>
       <c r="R3" t="n">
-        <v>6540083</v>
+        <v>6540040</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121142643</v>
+        <v>121142839</v>
       </c>
       <c r="B4" t="n">
-        <v>92021</v>
+        <v>98016</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,34 +907,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>223591</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -942,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479340</v>
+        <v>479191</v>
       </c>
       <c r="R4" t="n">
-        <v>6540076</v>
+        <v>6540041</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +987,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121142653</v>
+        <v>121142644</v>
       </c>
       <c r="B5" t="n">
-        <v>98013</v>
+        <v>98015</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223591</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479193</v>
+        <v>479335</v>
       </c>
       <c r="R5" t="n">
-        <v>6540040</v>
+        <v>6540083</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 28515-2022 artfynd.xlsx
+++ b/artfynd/A 28515-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121142643</v>
+        <v>121142644</v>
       </c>
       <c r="B2" t="n">
-        <v>92024</v>
+        <v>98015</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479340</v>
+        <v>479335</v>
       </c>
       <c r="R2" t="n">
-        <v>6540076</v>
+        <v>6540083</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121142653</v>
+        <v>121142643</v>
       </c>
       <c r="B3" t="n">
-        <v>98016</v>
+        <v>92024</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,35 +797,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223591</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479193</v>
+        <v>479340</v>
       </c>
       <c r="R3" t="n">
-        <v>6540040</v>
+        <v>6540076</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,6 +876,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121142839</v>
+        <v>121142653</v>
       </c>
       <c r="B4" t="n">
         <v>98016</v>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479191</v>
+        <v>479193</v>
       </c>
       <c r="R4" t="n">
-        <v>6540041</v>
+        <v>6540040</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121142644</v>
+        <v>121142839</v>
       </c>
       <c r="B5" t="n">
-        <v>98015</v>
+        <v>98016</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>223591</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479335</v>
+        <v>479191</v>
       </c>
       <c r="R5" t="n">
-        <v>6540083</v>
+        <v>6540041</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
